--- a/artfynd/A 53155-2022 artfynd.xlsx
+++ b/artfynd/A 53155-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115390597</v>
+        <v>76721947</v>
       </c>
       <c r="B2" t="n">
-        <v>56611</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,20 +711,19 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Korpberget, N, Vrm</t>
+          <t>Karlstad, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397484</v>
+        <v>397562</v>
       </c>
       <c r="R2" t="n">
-        <v>6583170</v>
+        <v>6583241</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,12 +747,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,59 +777,54 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Per Lif</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Lars Thornberg, Per Lif</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115390600</v>
+        <v>115390597</v>
       </c>
       <c r="B3" t="n">
-        <v>57943</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -892,6 +891,111 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>115390600</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Korpberget, N, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>397484</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6583170</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Segerstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-03-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-03-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53155-2022 artfynd.xlsx
+++ b/artfynd/A 53155-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76721947</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115390597</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,8 +1011,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115390600</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>